--- a/results/Int All Data -0.6/Rando_4_permute.xlsx
+++ b/results/Int All Data -0.6/Rando_4_permute.xlsx
@@ -440,1543 +440,1543 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8003839601799356</v>
+        <v>0.7894684307190558</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_5</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7960993876530342</v>
+        <v>0.7891551475110359</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>accy_svd_entropy</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7978438970539821</v>
+        <v>0.7908658594501906</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7974968163841689</v>
+        <v>0.7853866429629131</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>accy_n_below_mean</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.79814807421012</v>
+        <v>0.7856908201190511</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>accx_std</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7940077975822731</v>
+        <v>0.7876134228808466</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>accx_iqr_5_95</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7949814446681265</v>
+        <v>0.7862159941497119</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>accz_n_sign_changes</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.7995455029412548</v>
+        <v>0.7893579322817945</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>accx_n_above_mean</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.7985718558554016</v>
+        <v>0.7907800524228402</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>accy_peaks</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.7991217212959734</v>
+        <v>0.7914404163006734</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>accy_kurtosis</t>
+          <t>accz_iqr_5_95</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.7991217212959734</v>
+        <v>0.7941156692737994</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.8010014205440936</v>
+        <v>0.7941156692737994</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.8101204310384682</v>
+        <v>0.7925830506954923</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>accy_sum</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.8101542285002612</v>
+        <v>0.7887378451719013</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>accz_kurtosis</t>
+          <t>accx_energy</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.8101204310384682</v>
+        <v>0.7841984783086839</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>accx_rms</t>
+          <t>accz_pct_5</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.8178849163153832</v>
+        <v>0.7878993879332205</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>accx_energy</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.8307542192541162</v>
+        <v>0.7888392375572806</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.8363166160230089</v>
+        <v>0.7878655904714273</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.8309570040248749</v>
+        <v>0.7854269197308532</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.8334970671508284</v>
+        <v>0.7880774812940681</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.8353767663989488</v>
+        <v>0.7915911915058749</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>accz_peaks</t>
+          <t>accy_max</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.838755286763583</v>
+        <v>0.786026167991247</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>accz_ptp</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.837815437139523</v>
+        <v>0.7868893166398389</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.8394156506414163</v>
+        <v>0.786677425817198</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>accz_perm_entropy</t>
+          <t>accx_entropy</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.8425393766697347</v>
+        <v>0.7861184543247441</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.8428526598777548</v>
+        <v>0.7867112232789912</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>accy_mean</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.8472724222518286</v>
+        <v>0.7871596963341837</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.8469591390438085</v>
+        <v>0.7868802105879568</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>accx_max</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.848593150007495</v>
+        <v>0.7868802105879568</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.8478651912060755</v>
+        <v>0.7838578769450176</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>accy_entropy</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.8459516944961621</v>
+        <v>0.7838578769450176</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.8529791149197756</v>
+        <v>0.7841711601530377</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr_5_95</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.8614377615363171</v>
+        <v>0.7789467380020763</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>accy_lineintegral</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.8520054678339224</v>
+        <v>0.7790481303874555</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>accz_perm_entropy</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.8492873113471213</v>
+        <v>0.7804091349110619</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.8500152701485407</v>
+        <v>0.7800958517030419</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>accy_rms</t>
+          <t>accx_svd_entropy</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.8522420500664742</v>
+        <v>0.7824331300582367</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>accy_ptp</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.8603536160132024</v>
+        <v>0.7860053291417476</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>accz_n_below_mean</t>
+          <t>accz_lineintegral</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.8630717725000036</v>
+        <v>0.7860300205516586</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>accx_peaks</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.8639869307141526</v>
+        <v>0.7800074179299563</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>accx_n_below_mean</t>
+          <t>accz_sum</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.8643678088457589</v>
+        <v>0.7747089215492617</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.8625895019830179</v>
+        <v>0.7725835340167075</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_5</t>
+          <t>accx_peaks</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.8521250723230659</v>
+        <v>0.7698315800681133</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>accy_n_sign_changes</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.8522940596320314</v>
+        <v>0.7721779644751902</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_95</t>
+          <t>accx_skewness</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.8497201990442849</v>
+        <v>0.7712719123129231</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>accz_energy</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.8479939017471011</v>
+        <v>0.7714500056737708</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.8464274857070009</v>
+        <v>0.774201959622365</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.8388319877390513</v>
+        <v>0.7762350608214219</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>accx_entropy</t>
+          <t>accx_ptp</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.8368079925918765</v>
+        <v>0.7755929090473529</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.8389333801244307</v>
+        <v>0.774720654346879</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>accz_svd_entropy</t>
+          <t>accx_min</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.8284169408989215</v>
+        <v>0.7679883050275212</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>accz_mean</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.8302966401470417</v>
+        <v>0.7569804892331444</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>accz_iqr</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.8339026366923458</v>
+        <v>0.7569713831812623</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>accx_rms</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.8256896783602382</v>
+        <v>0.7543702044378695</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>accx_lineintegral</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.8218626849404114</v>
+        <v>0.7591123560718454</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr_5_95</t>
+          <t>accx_n_below_mean</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.8087385876653623</v>
+        <v>0.7607463670355318</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>accx_perm_entropy</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.824476822296098</v>
+        <v>0.7529701489609995</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>accz_skewness</t>
+          <t>accy_rms</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.824790105504118</v>
+        <v>0.746584880311455</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>accy_std</t>
+          <t>accx_kurtosis</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.8089907552559431</v>
+        <v>0.7443243029317285</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>accx_n_above_mean</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.8043682081111106</v>
+        <v>0.7387436940590717</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>accx_mean</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.8270597889357267</v>
+        <v>0.7403101100991719</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>accy_svd_entropy</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.8210398130597596</v>
+        <v>0.7425459960689874</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.8150536346455854</v>
+        <v>0.7387034172911316</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_95</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.816408159863045</v>
+        <v>0.7417660277020108</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>accz_lineintegral</t>
+          <t>accx_pct_5</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.7576058298345081</v>
+        <v>0.7298208139129265</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>accy_energy</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.7673760981548337</v>
+        <v>0.7328093500940724</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>accy_energy</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.8083915069955492</v>
+        <v>0.7050154032369913</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.8074516573714892</v>
+        <v>0.7076841769039703</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>accy_iqr_5_95</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.8074516573714892</v>
+        <v>0.7284363437940855</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.8074516573714892</v>
+        <v>0.723442024569529</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>accz_peaks</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.8074516573714892</v>
+        <v>0.7100123492072832</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>accz_mean</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.6804055975601384</v>
+        <v>0.7077088683138815</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>accz_entropy</t>
+          <t>accz_skewness</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.6653342061133829</v>
+        <v>0.7064219380200081</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.6579168015062811</v>
+        <v>0.7232677837690928</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>accz_rms</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.6421421426680172</v>
+        <v>0.7286391285648441</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>accz_n_below_mean</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.6393901887194229</v>
+        <v>0.7212152446515955</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.6424554258760372</v>
+        <v>0.7248720249477802</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.6339629817977027</v>
+        <v>0.7198256961576663</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.6370867078260212</v>
+        <v>0.7168826902359309</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>accz_sum</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.5384974103789378</v>
+        <v>0.7197854193897264</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.5384974103789378</v>
+        <v>0.7062583793188953</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.5380151398619523</v>
+        <v>0.7062583793188953</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.5236963986265272</v>
+        <v>0.7071982289429555</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.5221637800482201</v>
+        <v>0.7029565599297293</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>accx_kurtosis</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.5210458370633123</v>
+        <v>0.6535345140380298</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.5093620720330732</v>
+        <v>0.643131199995517</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>accx_skewness</t>
+          <t>accy_n_above_mean</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.5093620720330732</v>
+        <v>0.6309404730383813</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.5140275226915808</v>
+        <v>0.6217200701586274</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>accz_max</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.5035877844415398</v>
+        <v>0.628443313426103</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.5039010676495599</v>
+        <v>0.587227746560364</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>accx_lineintegral</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.5039010676495599</v>
+        <v>0.5947335849405515</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>accy_perm_entropy</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.5060108698240851</v>
+        <v>0.6140713368104442</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>accz_svd_entropy</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.5071288128089928</v>
+        <v>0.6257304104307723</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>accy_min</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.5032589158754909</v>
+        <v>0.6254509246845453</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.5029456326674708</v>
+        <v>0.5994913219325564</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.5029456326674708</v>
+        <v>0.6075599843656094</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.5035721990835109</v>
+        <v>0.5940888064207472</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.5023190662514307</v>
+        <v>0.5983889643056776</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>accz_n_above_mean</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.5023190662514307</v>
+        <v>0.575512810814067</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>accx_min</t>
+          <t>accx_max</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.5009554349820891</v>
+        <v>0.5800950811909595</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>accy_n_sign_changes</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.5009554349820891</v>
+        <v>0.5580638642441766</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.501234920728316</v>
+        <v>0.5583771474521967</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.5014806090127499</v>
+        <v>0.5642957309427846</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.5014806090127499</v>
+        <v>0.5733783172296308</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>accz_kurtosis</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.5017600947589769</v>
+        <v>0.5714310230579243</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>accy_sum</t>
+          <t>accy_n_below_mean</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.5072210991424901</v>
+        <v>0.5684606989805424</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.5091099044424925</v>
+        <v>0.5719159203206451</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>accy_iqr</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.5075096909405992</v>
+        <v>0.560037250756853</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>accz_n_sign_changes</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.5075096909405992</v>
+        <v>0.5602491415794937</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.5075096909405992</v>
+        <v>0.5624759214974272</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.5075096909405992</v>
+        <v>0.5624759214974272</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.5094231876505125</v>
+        <v>0.5596901700870398</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.5112690894368397</v>
+        <v>0.5722890933314281</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_5</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.5101147222444037</v>
+        <v>0.5609771003809132</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>accy_max</t>
+          <t>accy_min</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.5038919615976778</v>
+        <v>0.565092685598849</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>accy_peaks</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.5038919615976778</v>
+        <v>0.5679031284191474</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>accx_perm_entropy</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.5028169221264452</v>
+        <v>0.5694851298172765</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>accx_pct_95</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.4999635757924717</v>
+        <v>0.556585881977162</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>accx_svd_entropy</t>
+          <t>accy_pct_95</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.499472199223604</v>
+        <v>0.5377225203870493</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>accz_min</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.5003873574377531</v>
+        <v>0.4883628159274654</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>accx_iqr</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.5003873574377531</v>
+        <v>0.4895445012755477</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.4991862341712302</v>
+        <v>0.4895107038137546</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>accx_sum</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.5014130140891637</v>
+        <v>0.5055375302425992</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.5014130140891637</v>
+        <v>0.5020082346727635</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>accy_mean</t>
+          <t>accz_std</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.5046225471448325</v>
+        <v>0.5214396738072122</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>accz_std</t>
+          <t>accz_energy</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.5008111390830345</v>
+        <v>0.5156095240897101</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>accz_min</t>
+          <t>accz_rms</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.4906820572952785</v>
+        <v>0.5090761069806994</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.4915881094575455</v>
+        <v>0.5109896036906127</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>accz_ptp</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.4951200317731164</v>
+        <v>0.5173566602363932</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.4951200317731164</v>
+        <v>0.5190244686618727</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.4918246916900972</v>
+        <v>0.5150284879330803</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_95</t>
+          <t>accz_entropy</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.4658143051872274</v>
+        <v>0.5149946904712872</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>accy_skewness</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.462706164516938</v>
+        <v>0.5118956558528798</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>accx_sum</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.4663823827315634</v>
+        <v>0.5110234011524059</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>accx_ptp</t>
+          <t>accz_n_above_mean</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.4809494389971575</v>
+        <v>0.5061213682613466</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.4661925565730984</v>
+        <v>0.5061213682613466</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>accy_perm_entropy</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.4376121620428937</v>
+        <v>0.5013883226792526</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>accx_std</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.4225237843070505</v>
+        <v>0.5013883226792526</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>accy_n_above_mean</t>
+          <t>accz_max</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.4164335867617618</v>
+        <v>0.5000337974617931</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>accx_mean</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.4038787928457253</v>
+        <v>0.5000675949235862</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.4004391568636516</v>
+        <v>0.5000675949235862</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>accy_std</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.4004144654537405</v>
+        <v>0.5011088369330257</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>accy_lineintegral</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.4419214259797061</v>
+        <v>0.5011088369330257</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>accy_skewness</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.4509351915282897</v>
+        <v>0.5011088369330257</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>accz_pct_95</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.449537762797155</v>
+        <v>0.5010074445476463</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr_5_95</t>
+          <t>accy_ptp</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0.4989834494004715</v>
+        <v>0.50031328320802</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>accy_entropy</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.4989834494004715</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0.4989834494004715</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>accx_n_sign_changes</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.4989834494004715</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0.4989834494004715</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>accy_kurtosis</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0.4989496519386784</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>accy_pct_5</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>0.5000675949235862</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>accx_n_sign_changes</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>0.5000337974617931</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>0.5000337974617931</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B156" t="n">
